--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297505</v>
+        <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555825</v>
+        <v>555863</v>
       </c>
       <c r="R4" t="n">
-        <v>7045682</v>
+        <v>7045666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297267</v>
+        <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555863</v>
+        <v>555825</v>
       </c>
       <c r="R5" t="n">
-        <v>7045666</v>
+        <v>7045682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1775,38 +1775,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1815,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,7 +1889,7 @@
         <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,37 +1993,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,39 +2121,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R15" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,49 +2205,50 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2266,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R16" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,57 +2322,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R17" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2657,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,39 +3122,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R24" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,34 +3229,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R25" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,49 +3335,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R26" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,57 +3430,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R27" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R2" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R3" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297267</v>
+        <v>129297505</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555863</v>
+        <v>555825</v>
       </c>
       <c r="R4" t="n">
-        <v>7045666</v>
+        <v>7045682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297505</v>
+        <v>129297267</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555825</v>
+        <v>555863</v>
       </c>
       <c r="R5" t="n">
-        <v>7045682</v>
+        <v>7045666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,37 +1775,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,45 +1892,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,62 +1991,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
         <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>129298500</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,34 +2680,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R20" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2773,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297523</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,43 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555831</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045664</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,12 +2880,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
         <v>129298473</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1775,38 +1775,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1815,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,49 +1886,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555897</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,57 +1981,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2562,45 +2562,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R19" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296992</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,43 +2689,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555879</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045662</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,44 +2773,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,12 +2880,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -1775,37 +1775,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,45 +1892,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,62 +1991,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129297505</v>
+        <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555825</v>
+        <v>555863</v>
       </c>
       <c r="R4" t="n">
-        <v>7045682</v>
+        <v>7045666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129297267</v>
+        <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555863</v>
+        <v>555825</v>
       </c>
       <c r="R5" t="n">
-        <v>7045666</v>
+        <v>7045682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2562,54 +2562,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R19" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,7 +2672,7 @@
         <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,45 +2776,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R21" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R9" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R10" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
         <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R9" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R10" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
         <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,38 +2217,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298456</v>
+        <v>129297194</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2257,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555712</v>
+        <v>555908</v>
       </c>
       <c r="R16" t="n">
-        <v>7045648</v>
+        <v>7045697</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,49 +2316,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R17" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2413,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2562,45 +2562,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R19" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,54 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,38 +1775,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1815,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,49 +1886,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>97581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555897</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,57 +1981,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>97577</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296981</v>
+        <v>129298456</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,34 +2121,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555873</v>
+        <v>555712</v>
       </c>
       <c r="R15" t="n">
-        <v>7045669</v>
+        <v>7045648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,12 +2215,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2220,7 +2230,7 @@
         <v>129297194</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,39 +2349,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R17" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,12 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296992</v>
+        <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,43 +2573,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555879</v>
+        <v>555831</v>
       </c>
       <c r="R19" t="n">
-        <v>7045662</v>
+        <v>7045664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,22 +2657,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,34 +2680,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R20" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,12 +2773,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
         <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -1775,37 +1775,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,45 +1892,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97581</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,62 +1991,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>97581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R2" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R3" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,49 +1892,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555897</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,57 +1987,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>97581</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,50 +2098,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298456</v>
+        <v>129297194</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2150,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555712</v>
+        <v>555908</v>
       </c>
       <c r="R15" t="n">
-        <v>7045648</v>
+        <v>7045697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,61 +2209,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129297194</v>
+        <v>129296981</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555908</v>
+        <v>555873</v>
       </c>
       <c r="R16" t="n">
-        <v>7045697</v>
+        <v>7045669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296981</v>
+        <v>129298456</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,34 +2339,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555873</v>
+        <v>555712</v>
       </c>
       <c r="R17" t="n">
-        <v>7045669</v>
+        <v>7045648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2413,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
         <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,54 +2669,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R20" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,45 +2776,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R21" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1775,50 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>97587</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,57 +1870,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,49 +1981,50 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,49 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129297194</v>
+        <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555908</v>
+        <v>555873</v>
       </c>
       <c r="R15" t="n">
-        <v>7045697</v>
+        <v>7045669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,45 +2217,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R16" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,34 +2573,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2666,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>91549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,66 +2773,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>92831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>129297222</v>
       </c>
       <c r="B12" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,37 +1882,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1921,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1967,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,38 +1999,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2217,37 +2217,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2256,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R16" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,50 +2322,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298456</v>
+        <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555712</v>
+        <v>555908</v>
       </c>
       <c r="R17" t="n">
-        <v>7045648</v>
+        <v>7045697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,12 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129296992</v>
+        <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,43 +2573,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555879</v>
+        <v>555831</v>
       </c>
       <c r="R19" t="n">
-        <v>7045662</v>
+        <v>7045664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,44 +2657,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>91549</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R20" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,57 +2764,66 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>92831</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R21" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R2" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R3" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R9" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R10" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1775,45 +1775,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R12" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,62 +1874,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R13" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,12 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,49 +1981,50 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2669,45 +2669,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,54 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3335,45 +3335,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R26" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,61 +3434,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R27" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,34 +3122,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R24" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,7 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,39 +3239,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R25" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R9" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R10" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1775,37 +1775,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,7 +1895,7 @@
         <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,38 +1999,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,54 +2669,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R20" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,45 +2776,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297219</v>
+        <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555906</v>
+        <v>555879</v>
       </c>
       <c r="R21" t="n">
-        <v>7045694</v>
+        <v>7045662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,39 +3122,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R24" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,34 +3229,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R25" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,49 +3335,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R26" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,57 +3430,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R27" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R9" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R10" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1775,50 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,57 +1870,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,49 +1981,50 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,45 +2110,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R15" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,39 +2232,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R16" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,49 +2316,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R17" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2413,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,34 +3122,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R24" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,7 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,39 +3239,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R25" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3551,6 +3551,719 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129603480</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555867</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7045737</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129603348</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555874</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7045798</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129603442</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555887</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7045779</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129603212</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91851</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>658</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>555874</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7045791</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129603470</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>555881</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7045771</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129603400</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>555884</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7045784</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129603550</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78447</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>555868</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7045740</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R9" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R10" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1882,37 +1882,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1921,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1967,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,38 +1999,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2033,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,49 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129297194</v>
+        <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555908</v>
+        <v>555873</v>
       </c>
       <c r="R15" t="n">
-        <v>7045697</v>
+        <v>7045669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,10 +2217,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296981</v>
+        <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,34 +2228,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555873</v>
+        <v>555712</v>
       </c>
       <c r="R16" t="n">
-        <v>7045669</v>
+        <v>7045648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,50 +2322,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298456</v>
+        <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555712</v>
+        <v>555908</v>
       </c>
       <c r="R17" t="n">
-        <v>7045648</v>
+        <v>7045697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,12 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2657,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,39 +3122,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R24" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,34 +3229,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R25" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -1775,45 +1775,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R12" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,12 +1874,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1999,49 +2003,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R19" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,22 +2657,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B20" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,34 +2680,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R20" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,66 +2773,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R2" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R3" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1775,37 +1775,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,50 +1892,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R13" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,57 +1987,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296981</v>
+        <v>129298456</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,34 +2121,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555873</v>
+        <v>555712</v>
       </c>
       <c r="R15" t="n">
-        <v>7045669</v>
+        <v>7045648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,22 +2215,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,39 +2238,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R16" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,12 +2322,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,12 +2657,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R21" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,12 +2880,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,34 +3122,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R24" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,7 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,39 +3239,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R25" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,45 +3335,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R26" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,61 +3434,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R27" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>91851</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,22 +3963,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>91851</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4043,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1892,45 +1892,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,61 +1991,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,39 +2121,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R15" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,22 +2205,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296981</v>
+        <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,34 +2228,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555873</v>
+        <v>555712</v>
       </c>
       <c r="R16" t="n">
-        <v>7045669</v>
+        <v>7045648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,12 +2322,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R19" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,66 +2657,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R20" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2787,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R21" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,12 +2880,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,39 +3122,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R24" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,34 +3229,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R25" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,49 +3335,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R26" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,57 +3430,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R27" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>91851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R31" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,19 +3936,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,44 +3953,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603212</v>
+        <v>129603400</v>
       </c>
       <c r="B32" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4000,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555874</v>
+        <v>555884</v>
       </c>
       <c r="R32" t="n">
-        <v>7045791</v>
+        <v>7045784</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4072,32 +4062,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603400</v>
+        <v>129603470</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,13 +4097,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555884</v>
+        <v>555881</v>
       </c>
       <c r="R33" t="n">
-        <v>7045784</v>
+        <v>7045771</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4140,9 +4130,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,50 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>97627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,49 +1870,50 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1931,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R13" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1967,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,45 +1999,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129297154</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555901</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,57 +2098,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R15" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,39 +2232,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R16" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,49 +2316,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2373,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R17" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2403,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2413,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
         <v>129298500</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>92863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2657,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>91581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
         <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129298473</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,34 +3122,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R24" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,7 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,39 +3239,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R25" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,7 +3338,7 @@
         <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129603442</v>
       </c>
       <c r="B30" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603400</v>
       </c>
       <c r="B31" t="n">
-        <v>91851</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555884</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045784</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3965,32 +3965,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603400</v>
+        <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>78827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555884</v>
+        <v>555881</v>
       </c>
       <c r="R32" t="n">
-        <v>7045784</v>
+        <v>7045771</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,9 +4033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,22 +4060,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B33" t="n">
-        <v>78801</v>
+        <v>91879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,21 +4083,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4097,13 +4107,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R33" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4130,19 +4140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78447</v>
+        <v>78473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -1882,38 +1882,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129296765</v>
+        <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1922,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555812</v>
+        <v>555901</v>
       </c>
       <c r="R13" t="n">
-        <v>7045625</v>
+        <v>7045680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1967,12 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,37 +1993,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297154</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555901</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045680</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R2" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R3" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B9" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R9" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R10" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,45 +1775,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297222</v>
+        <v>129296765</v>
       </c>
       <c r="B12" t="n">
-        <v>97627</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555897</v>
+        <v>555812</v>
       </c>
       <c r="R12" t="n">
-        <v>7045684</v>
+        <v>7045625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1860,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,12 +1880,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1885,7 +1895,7 @@
         <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,50 +2003,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>97639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R14" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,12 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,49 +2098,50 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2149,10 +2150,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R15" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,57 +2215,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R16" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2301,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2311,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,39 +2349,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R17" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2413,12 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,12 +2433,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
         <v>129298500</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,32 +2562,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>91587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R19" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2657,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297523</v>
+        <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>91581</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555831</v>
+        <v>555906</v>
       </c>
       <c r="R20" t="n">
-        <v>7045664</v>
+        <v>7045694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,12 +2764,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
         <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129298473</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,39 +3122,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R24" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,34 +3229,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R25" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,45 +3335,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B26" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R26" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,61 +3434,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R27" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129603442</v>
       </c>
       <c r="B30" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129603400</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>78827</v>
+        <v>91885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4033,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,22 +4050,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B33" t="n">
-        <v>91879</v>
+        <v>78832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,21 +4073,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,13 +4097,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R33" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4140,9 +4130,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129297020</v>
+        <v>129296695</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555890</v>
+        <v>555751</v>
       </c>
       <c r="R2" t="n">
-        <v>7045654</v>
+        <v>7045603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,38 +792,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296695</v>
+        <v>129297020</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555751</v>
+        <v>555890</v>
       </c>
       <c r="R3" t="n">
-        <v>7045603</v>
+        <v>7045654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
         <v>129297267</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129297505</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>129297553</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>129297616</v>
       </c>
       <c r="B7" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129297080</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129297227</v>
+        <v>129297184</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555865</v>
+        <v>555885</v>
       </c>
       <c r="R9" t="n">
-        <v>7045702</v>
+        <v>7045677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129297184</v>
+        <v>129297227</v>
       </c>
       <c r="B10" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555885</v>
+        <v>555865</v>
       </c>
       <c r="R10" t="n">
-        <v>7045677</v>
+        <v>7045702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
         <v>129297139</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,50 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129296765</v>
+        <v>129297222</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>97640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555812</v>
+        <v>555897</v>
       </c>
       <c r="R12" t="n">
-        <v>7045625</v>
+        <v>7045684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,12 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,12 +1870,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1895,7 +1885,7 @@
         <v>129297154</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,45 +1993,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297222</v>
+        <v>129296765</v>
       </c>
       <c r="B14" t="n">
-        <v>97639</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555897</v>
+        <v>555812</v>
       </c>
       <c r="R14" t="n">
-        <v>7045684</v>
+        <v>7045625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2078,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298456</v>
+        <v>129296981</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,39 +2121,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555712</v>
+        <v>555873</v>
       </c>
       <c r="R15" t="n">
-        <v>7045648</v>
+        <v>7045669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,49 +2205,50 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129297194</v>
+        <v>129298456</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2266,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555908</v>
+        <v>555712</v>
       </c>
       <c r="R16" t="n">
-        <v>7045697</v>
+        <v>7045648</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2311,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,57 +2322,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129296981</v>
+        <v>129297194</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555873</v>
+        <v>555908</v>
       </c>
       <c r="R17" t="n">
-        <v>7045669</v>
+        <v>7045697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,7 +2448,7 @@
         <v>129298500</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>129297523</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>129297219</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129296992</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129298473</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>129297180</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129297577</v>
+        <v>129297079</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,34 +3122,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555799</v>
+        <v>555901</v>
       </c>
       <c r="R24" t="n">
-        <v>7045679</v>
+        <v>7045697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3191,7 +3196,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129297079</v>
+        <v>129297577</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3229,39 +3239,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555901</v>
+        <v>555799</v>
       </c>
       <c r="R25" t="n">
-        <v>7045697</v>
+        <v>7045679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,49 +3335,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129296790</v>
+        <v>129298378</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555823</v>
+        <v>555730</v>
       </c>
       <c r="R26" t="n">
-        <v>7045642</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,57 +3430,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298378</v>
+        <v>129296790</v>
       </c>
       <c r="B27" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555730</v>
+        <v>555823</v>
       </c>
       <c r="R27" t="n">
-        <v>7045711</v>
+        <v>7045642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,12 +3541,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129603442</v>
       </c>
       <c r="B30" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603400</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>78833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555884</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045784</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,12 +3963,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3968,7 +3978,7 @@
         <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,32 +4072,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>78832</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4097,13 +4107,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R33" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4130,19 +4140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129297523</v>
+        <v>129296992</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,34 +2573,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555831</v>
+        <v>555879</v>
       </c>
       <c r="R19" t="n">
-        <v>7045664</v>
+        <v>7045662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,44 +2666,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129297219</v>
+        <v>129297523</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>91588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555906</v>
+        <v>555831</v>
       </c>
       <c r="R20" t="n">
-        <v>7045694</v>
+        <v>7045664</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,66 +2773,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129296992</v>
+        <v>129297219</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>92870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555879</v>
+        <v>555906</v>
       </c>
       <c r="R21" t="n">
-        <v>7045662</v>
+        <v>7045694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>78833</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R31" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,19 +3936,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,22 +3953,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>91886</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R32" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4043,9 +4033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
         <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,22 +3963,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4043,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R31" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,19 +3936,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,12 +3953,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4072,32 +4062,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603400</v>
+        <v>129603470</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,13 +4097,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555884</v>
+        <v>555881</v>
       </c>
       <c r="R33" t="n">
-        <v>7045784</v>
+        <v>7045771</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4140,9 +4130,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603400</v>
+        <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555884</v>
+        <v>555874</v>
       </c>
       <c r="R31" t="n">
-        <v>7045784</v>
+        <v>7045791</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R32" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,9 +4033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,44 +4060,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4097,13 +4107,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R33" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4130,19 +4140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,22 +3963,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>91895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4043,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
         <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603470</v>
+        <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>91897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555881</v>
+        <v>555874</v>
       </c>
       <c r="R31" t="n">
-        <v>7045771</v>
+        <v>7045791</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,19 +3936,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,22 +3953,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>91895</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R32" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4043,9 +4033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,12 +4060,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4075,7 +4075,7 @@
         <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>91897</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,44 +3963,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4043,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,44 +4060,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603400</v>
+        <v>129603212</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555884</v>
+        <v>555874</v>
       </c>
       <c r="R33" t="n">
-        <v>7045784</v>
+        <v>7045791</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R31" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,19 +3936,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,44 +3953,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603400</v>
+        <v>129603212</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4000,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555884</v>
+        <v>555874</v>
       </c>
       <c r="R32" t="n">
-        <v>7045784</v>
+        <v>7045791</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4072,10 +4062,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B33" t="n">
-        <v>91897</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,21 +4073,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,13 +4097,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R33" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4140,9 +4130,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,32 +3868,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603400</v>
+        <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>91897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555884</v>
+        <v>555874</v>
       </c>
       <c r="R31" t="n">
-        <v>7045784</v>
+        <v>7045791</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>91897</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,21 +3976,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4000,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R32" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,9 +4033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,44 +4060,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4097,13 +4107,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R33" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4130,19 +4140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,12 +4157,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129603442</v>
       </c>
       <c r="B30" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>78487</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129603480</v>
       </c>
       <c r="B28" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129603348</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129603442</v>
       </c>
       <c r="B30" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129603212</v>
       </c>
       <c r="B31" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129603470</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>129603400</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129603550</v>
       </c>
       <c r="B34" t="n">
-        <v>78487</v>
+        <v>78490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 42124-2025 artfynd.xlsx
+++ b/artfynd/A 42124-2025 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129603212</v>
+        <v>129603470</v>
       </c>
       <c r="B31" t="n">
-        <v>91903</v>
+        <v>78844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3903,13 +3903,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555874</v>
+        <v>555881</v>
       </c>
       <c r="R31" t="n">
-        <v>7045791</v>
+        <v>7045771</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,9 +3936,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,44 +3963,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129603470</v>
+        <v>129603400</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555881</v>
+        <v>555884</v>
       </c>
       <c r="R32" t="n">
-        <v>7045771</v>
+        <v>7045784</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4033,19 +4043,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,44 +4060,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129603400</v>
+        <v>129603212</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>91903</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555884</v>
+        <v>555874</v>
       </c>
       <c r="R33" t="n">
-        <v>7045784</v>
+        <v>7045791</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
